--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/114.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/114.xlsx
@@ -426,13 +426,13 @@
         <v>-1.729084885752891</v>
       </c>
       <c r="E2">
-        <v>-20.07100041860198</v>
+        <v>-12.48039040084096</v>
       </c>
       <c r="F2">
-        <v>-6.766382585038453</v>
+        <v>-7.16882522188739</v>
       </c>
       <c r="G2">
-        <v>-14.64491773201645</v>
+        <v>-11.73752380742663</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.230926349293673</v>
       </c>
       <c r="E3">
-        <v>-20.10437527203851</v>
+        <v>-14.27808589850991</v>
       </c>
       <c r="F3">
-        <v>-6.760404095207669</v>
+        <v>-6.362801659562794</v>
       </c>
       <c r="G3">
-        <v>-15.04444760987785</v>
+        <v>-11.52467559252473</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.765567349406314</v>
       </c>
       <c r="E4">
-        <v>-21.5814548099644</v>
+        <v>-14.75896002491042</v>
       </c>
       <c r="F4">
-        <v>-7.1670926476159</v>
+        <v>-6.781810256213706</v>
       </c>
       <c r="G4">
-        <v>-14.63550419577553</v>
+        <v>-11.59292579936234</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.216585127996671</v>
       </c>
       <c r="E5">
-        <v>-20.90204332611961</v>
+        <v>-16.10547007177314</v>
       </c>
       <c r="F5">
-        <v>-6.704152840723654</v>
+        <v>-7.102228804437246</v>
       </c>
       <c r="G5">
-        <v>-14.37847675065206</v>
+        <v>-12.30841414349179</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.556754131450112</v>
       </c>
       <c r="E6">
-        <v>-22.23392640193756</v>
+        <v>-16.57025905849841</v>
       </c>
       <c r="F6">
-        <v>-6.892175949975329</v>
+        <v>-6.946214371368996</v>
       </c>
       <c r="G6">
-        <v>-14.48017008852739</v>
+        <v>-12.8045093241882</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.741204412454335</v>
       </c>
       <c r="E7">
-        <v>-22.54005577333009</v>
+        <v>-17.44558591333704</v>
       </c>
       <c r="F7">
-        <v>-6.853710504774657</v>
+        <v>-6.720733845731827</v>
       </c>
       <c r="G7">
-        <v>-14.97592097248771</v>
+        <v>-12.30431568811417</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.752814222752658</v>
       </c>
       <c r="E8">
-        <v>-25.03550307457489</v>
+        <v>-17.17205702632574</v>
       </c>
       <c r="F8">
-        <v>-6.773846591017919</v>
+        <v>-6.304214438853506</v>
       </c>
       <c r="G8">
-        <v>-14.9349380739843</v>
+        <v>-12.79200870423191</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.582166067601496</v>
       </c>
       <c r="E9">
-        <v>-24.86823935862758</v>
+        <v>-19.17174057863281</v>
       </c>
       <c r="F9">
-        <v>-6.591399314368028</v>
+        <v>-6.587144292499721</v>
       </c>
       <c r="G9">
-        <v>-15.03052014479414</v>
+        <v>-12.14679662081011</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.239778123857394</v>
       </c>
       <c r="E10">
-        <v>-24.77362595118532</v>
+        <v>-19.23740345174403</v>
       </c>
       <c r="F10">
-        <v>-6.835358124700067</v>
+        <v>-6.514855640063008</v>
       </c>
       <c r="G10">
-        <v>-14.37302924796719</v>
+        <v>-11.8411505038969</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.747806136124909</v>
       </c>
       <c r="E11">
-        <v>-25.17233544519066</v>
+        <v>-19.8540457573685</v>
       </c>
       <c r="F11">
-        <v>-6.256460558458781</v>
+        <v>-6.689209783558526</v>
       </c>
       <c r="G11">
-        <v>-14.21064036817486</v>
+        <v>-11.79976537411047</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.145344481236098</v>
       </c>
       <c r="E12">
-        <v>-25.27692508087181</v>
+        <v>-21.66340660408121</v>
       </c>
       <c r="F12">
-        <v>-6.610909383466804</v>
+        <v>-6.298836173564673</v>
       </c>
       <c r="G12">
-        <v>-14.28816341306797</v>
+        <v>-11.54384034065157</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.478423463003782</v>
       </c>
       <c r="E13">
-        <v>-25.76111405024593</v>
+        <v>-21.11230037429575</v>
       </c>
       <c r="F13">
-        <v>-6.286420711040585</v>
+        <v>-6.43596055840004</v>
       </c>
       <c r="G13">
-        <v>-13.29265588504481</v>
+        <v>-10.83080180022118</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.8026477323265648</v>
       </c>
       <c r="E14">
-        <v>-27.55549017646726</v>
+        <v>-22.11308407304288</v>
       </c>
       <c r="F14">
-        <v>-6.401190690953046</v>
+        <v>-6.273943088059317</v>
       </c>
       <c r="G14">
-        <v>-12.76363732896035</v>
+        <v>-10.01730806594716</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.1730730717155164</v>
       </c>
       <c r="E15">
-        <v>-26.82126151475962</v>
+        <v>-22.14130552305868</v>
       </c>
       <c r="F15">
-        <v>-6.264325637961332</v>
+        <v>-5.917492458774178</v>
       </c>
       <c r="G15">
-        <v>-12.11980243248289</v>
+        <v>-9.545330209504341</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.3605773090309676</v>
       </c>
       <c r="E16">
-        <v>-28.19800365409755</v>
+        <v>-24.08306536433365</v>
       </c>
       <c r="F16">
-        <v>-5.953476632731835</v>
+        <v>-5.589555266717089</v>
       </c>
       <c r="G16">
-        <v>-11.80109290287172</v>
+        <v>-8.596011412845092</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.7562202102390108</v>
       </c>
       <c r="E17">
-        <v>-28.20097433304658</v>
+        <v>-24.45145219638362</v>
       </c>
       <c r="F17">
-        <v>-6.34824225515568</v>
+        <v>-5.717992232753312</v>
       </c>
       <c r="G17">
-        <v>-11.6470002502008</v>
+        <v>-7.983848505541839</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.9878849424306966</v>
       </c>
       <c r="E18">
-        <v>-28.9556762257429</v>
+        <v>-25.12140369802639</v>
       </c>
       <c r="F18">
-        <v>-5.784010597544322</v>
+        <v>-5.464305508835687</v>
       </c>
       <c r="G18">
-        <v>-10.51188370624103</v>
+        <v>-8.128519345607989</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.046295126254004</v>
       </c>
       <c r="E19">
-        <v>-29.4138128841509</v>
+        <v>-25.39015051648559</v>
       </c>
       <c r="F19">
-        <v>-5.325831806560366</v>
+        <v>-4.806681921537907</v>
       </c>
       <c r="G19">
-        <v>-10.90041926236652</v>
+        <v>-8.071922259068609</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.9403883875090354</v>
       </c>
       <c r="E20">
-        <v>-32.12364720186683</v>
+        <v>-26.01050164232235</v>
       </c>
       <c r="F20">
-        <v>-5.098825776200148</v>
+        <v>-4.717152650579242</v>
       </c>
       <c r="G20">
-        <v>-10.91121826191562</v>
+        <v>-7.809703878539556</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.6960253463114122</v>
       </c>
       <c r="E21">
-        <v>-32.10583671359466</v>
+        <v>-27.08177103899887</v>
       </c>
       <c r="F21">
-        <v>-5.10288481446142</v>
+        <v>-4.834695303623158</v>
       </c>
       <c r="G21">
-        <v>-10.96197554612373</v>
+        <v>-7.586834642290281</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.3477848566939838</v>
       </c>
       <c r="E22">
-        <v>-32.21414196219911</v>
+        <v>-28.81483615563035</v>
       </c>
       <c r="F22">
-        <v>-4.958626626329957</v>
+        <v>-3.867085038966837</v>
       </c>
       <c r="G22">
-        <v>-10.4152058448577</v>
+        <v>-7.806439680637835</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.06342639479067623</v>
       </c>
       <c r="E23">
-        <v>-32.57147705343337</v>
+        <v>-29.38926855502933</v>
       </c>
       <c r="F23">
-        <v>-4.449720943021517</v>
+        <v>-4.187093407358279</v>
       </c>
       <c r="G23">
-        <v>-10.97133114781771</v>
+        <v>-7.603251637619526</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.4996665855254627</v>
       </c>
       <c r="E24">
-        <v>-33.67828591412209</v>
+        <v>-29.9325292035965</v>
       </c>
       <c r="F24">
-        <v>-4.327500022703394</v>
+        <v>-4.037326298199958</v>
       </c>
       <c r="G24">
-        <v>-10.76477627998596</v>
+        <v>-7.762058507138366</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.9275492471316866</v>
       </c>
       <c r="E25">
-        <v>-33.28512832925016</v>
+        <v>-29.26044252645912</v>
       </c>
       <c r="F25">
-        <v>-4.382863214095326</v>
+        <v>-3.469408565070415</v>
       </c>
       <c r="G25">
-        <v>-10.78735751110933</v>
+        <v>-8.52956876387192</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.320434529204001</v>
       </c>
       <c r="E26">
-        <v>-33.74196531561795</v>
+        <v>-29.94518855268495</v>
       </c>
       <c r="F26">
-        <v>-3.944933686946179</v>
+        <v>-3.173762344776179</v>
       </c>
       <c r="G26">
-        <v>-10.83291392827524</v>
+        <v>-8.388261438073668</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.663384208011839</v>
       </c>
       <c r="E27">
-        <v>-33.58667488494692</v>
+        <v>-29.2496874006909</v>
       </c>
       <c r="F27">
-        <v>-3.995970985630088</v>
+        <v>-2.994101202758024</v>
       </c>
       <c r="G27">
-        <v>-10.82460445897167</v>
+        <v>-9.36149892625415</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.947076295206407</v>
       </c>
       <c r="E28">
-        <v>-33.97373035109351</v>
+        <v>-31.21784598119358</v>
       </c>
       <c r="F28">
-        <v>-4.119070070878323</v>
+        <v>-3.031302454711696</v>
       </c>
       <c r="G28">
-        <v>-11.14546584318337</v>
+        <v>-8.288107503874096</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.171354722740873</v>
       </c>
       <c r="E29">
-        <v>-33.94629459131804</v>
+        <v>-31.03031960829895</v>
       </c>
       <c r="F29">
-        <v>-3.699682572587141</v>
+        <v>-2.744215373037453</v>
       </c>
       <c r="G29">
-        <v>-11.797534066417</v>
+        <v>-9.499700960336565</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.341056744382777</v>
       </c>
       <c r="E30">
-        <v>-34.35164962092963</v>
+        <v>-29.81951660626108</v>
       </c>
       <c r="F30">
-        <v>-3.940393202086614</v>
+        <v>-3.575369576754722</v>
       </c>
       <c r="G30">
-        <v>-11.46434752116259</v>
+        <v>-8.90376303672128</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.462145781510694</v>
       </c>
       <c r="E31">
-        <v>-32.33004825442544</v>
+        <v>-30.38518867269222</v>
       </c>
       <c r="F31">
-        <v>-4.111786607373217</v>
+        <v>-3.150440691465417</v>
       </c>
       <c r="G31">
-        <v>-11.51634957049346</v>
+        <v>-10.52636072188427</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.544241342287953</v>
       </c>
       <c r="E32">
-        <v>-33.07763817869271</v>
+        <v>-29.26908285486575</v>
       </c>
       <c r="F32">
-        <v>-3.986686509700824</v>
+        <v>-2.88853136643483</v>
       </c>
       <c r="G32">
-        <v>-11.87297808871145</v>
+        <v>-9.108447446323339</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.59330734307302</v>
       </c>
       <c r="E33">
-        <v>-33.251384405182</v>
+        <v>-29.07540907850571</v>
       </c>
       <c r="F33">
-        <v>-3.951982761975799</v>
+        <v>-3.180341059148914</v>
       </c>
       <c r="G33">
-        <v>-11.12415586154708</v>
+        <v>-8.500992134776929</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.612128866411692</v>
       </c>
       <c r="E34">
-        <v>-31.59271758802254</v>
+        <v>-30.37808576121119</v>
       </c>
       <c r="F34">
-        <v>-4.129125019735448</v>
+        <v>-3.480659211893697</v>
       </c>
       <c r="G34">
-        <v>-11.14564130209695</v>
+        <v>-8.878225488431342</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.601075303925612</v>
       </c>
       <c r="E35">
-        <v>-32.48746933211708</v>
+        <v>-28.09891158586171</v>
       </c>
       <c r="F35">
-        <v>-4.398288509711706</v>
+        <v>-3.134546618898067</v>
       </c>
       <c r="G35">
-        <v>-10.63767119455118</v>
+        <v>-8.434685218170868</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.558540649089107</v>
       </c>
       <c r="E36">
-        <v>-31.41199751156143</v>
+        <v>-29.15904999342738</v>
       </c>
       <c r="F36">
-        <v>-4.018677369192701</v>
+        <v>-3.461668202408704</v>
       </c>
       <c r="G36">
-        <v>-10.82167131562388</v>
+        <v>-8.886038375904022</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.483271942556365</v>
       </c>
       <c r="E37">
-        <v>-31.73282630958286</v>
+        <v>-27.19033214638475</v>
       </c>
       <c r="F37">
-        <v>-4.39764790066891</v>
+        <v>-3.325663497655553</v>
       </c>
       <c r="G37">
-        <v>-10.44615613510434</v>
+        <v>-8.295569473519613</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.374849853756868</v>
       </c>
       <c r="E38">
-        <v>-31.33322470619801</v>
+        <v>-26.92550245794218</v>
       </c>
       <c r="F38">
-        <v>-4.247115861553433</v>
+        <v>-3.323736919409421</v>
       </c>
       <c r="G38">
-        <v>-10.69692002806752</v>
+        <v>-8.318591007199705</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.235464980898755</v>
       </c>
       <c r="E39">
-        <v>-30.72025272875675</v>
+        <v>-26.90786405168231</v>
       </c>
       <c r="F39">
-        <v>-4.493285525343426</v>
+        <v>-3.511313423592942</v>
       </c>
       <c r="G39">
-        <v>-10.87651381302744</v>
+        <v>-8.198706221586079</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.068630384332162</v>
       </c>
       <c r="E40">
-        <v>-30.25067035229437</v>
+        <v>-24.89198214784979</v>
       </c>
       <c r="F40">
-        <v>-4.395197907617725</v>
+        <v>-3.749114785325753</v>
       </c>
       <c r="G40">
-        <v>-10.22740852805146</v>
+        <v>-8.296023018258493</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.880448221404256</v>
       </c>
       <c r="E41">
-        <v>-29.61608396841451</v>
+        <v>-26.32005001159066</v>
       </c>
       <c r="F41">
-        <v>-4.726445836891041</v>
+        <v>-3.188619881821874</v>
       </c>
       <c r="G41">
-        <v>-10.72781403904</v>
+        <v>-7.434589274030277</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.679012290268224</v>
       </c>
       <c r="E42">
-        <v>-29.55935803875742</v>
+        <v>-26.27903109402919</v>
       </c>
       <c r="F42">
-        <v>-4.549852333231092</v>
+        <v>-3.364320967198473</v>
       </c>
       <c r="G42">
-        <v>-10.02093311331266</v>
+        <v>-7.636661663201852</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.471717582817103</v>
       </c>
       <c r="E43">
-        <v>-28.7439021387742</v>
+        <v>-25.47525865698575</v>
       </c>
       <c r="F43">
-        <v>-4.417093433751634</v>
+        <v>-3.784608010449624</v>
       </c>
       <c r="G43">
-        <v>-10.08071494466082</v>
+        <v>-7.465976556288108</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.268240169333785</v>
       </c>
       <c r="E44">
-        <v>-28.16497296468561</v>
+        <v>-24.71673926070097</v>
       </c>
       <c r="F44">
-        <v>-4.440073798437618</v>
+        <v>-3.986933567823633</v>
       </c>
       <c r="G44">
-        <v>-10.33443515479056</v>
+        <v>-6.958777805852987</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.075671836744076</v>
       </c>
       <c r="E45">
-        <v>-28.30160155397103</v>
+        <v>-23.94412725330431</v>
       </c>
       <c r="F45">
-        <v>-4.476166456250483</v>
+        <v>-3.941194557279826</v>
       </c>
       <c r="G45">
-        <v>-10.63580735741257</v>
+        <v>-7.647132918742567</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.8977133597733328</v>
       </c>
       <c r="E46">
-        <v>-28.28031772613498</v>
+        <v>-23.87562049851627</v>
       </c>
       <c r="F46">
-        <v>-4.199017129195622</v>
+        <v>-3.765701729231108</v>
       </c>
       <c r="G46">
-        <v>-9.733465201955582</v>
+        <v>-7.355520204370324</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.7368750561921219</v>
       </c>
       <c r="E47">
-        <v>-27.60089265686816</v>
+        <v>-23.47420750552836</v>
       </c>
       <c r="F47">
-        <v>-4.66814091176118</v>
+        <v>-3.923392119084371</v>
       </c>
       <c r="G47">
-        <v>-10.4185693591256</v>
+        <v>-7.546899531450053</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.5924035821049584</v>
       </c>
       <c r="E48">
-        <v>-27.14953965252366</v>
+        <v>-22.60301061898472</v>
       </c>
       <c r="F48">
-        <v>-4.359177308424013</v>
+        <v>-3.894733376838579</v>
       </c>
       <c r="G48">
-        <v>-10.12017995803447</v>
+        <v>-7.195935356649757</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.4640297342532175</v>
       </c>
       <c r="E49">
-        <v>-26.81993467187537</v>
+        <v>-22.71847312075829</v>
       </c>
       <c r="F49">
-        <v>-4.701734481639481</v>
+        <v>-3.978684835563067</v>
       </c>
       <c r="G49">
-        <v>-10.73107823694172</v>
+        <v>-7.198401713076514</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.3526901354701786</v>
       </c>
       <c r="E50">
-        <v>-26.67107467429523</v>
+        <v>-21.84743925927893</v>
       </c>
       <c r="F50">
-        <v>-4.803006931961129</v>
+        <v>-3.995585353239679</v>
       </c>
       <c r="G50">
-        <v>-10.0877862699327</v>
+        <v>-7.558393745562402</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.2582385095248663</v>
       </c>
       <c r="E51">
-        <v>-25.53445486921402</v>
+        <v>-22.19287125658402</v>
       </c>
       <c r="F51">
-        <v>-4.667315009126278</v>
+        <v>-4.037630369735723</v>
       </c>
       <c r="G51">
-        <v>-10.20509214057124</v>
+        <v>-7.51924985510606</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.1821948499011486</v>
       </c>
       <c r="E52">
-        <v>-24.82648229980285</v>
+        <v>-20.55081941055871</v>
       </c>
       <c r="F52">
-        <v>-4.673992705118728</v>
+        <v>-4.250341870503183</v>
       </c>
       <c r="G52">
-        <v>-10.50138265579047</v>
+        <v>-7.311605817791892</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.1259342489347892</v>
       </c>
       <c r="E53">
-        <v>-24.27719198809446</v>
+        <v>-20.26196616750544</v>
       </c>
       <c r="F53">
-        <v>-4.594093157978893</v>
+        <v>-4.302829843805635</v>
       </c>
       <c r="G53">
-        <v>-10.37510189619497</v>
+        <v>-6.607194559036848</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.09038780962712975</v>
       </c>
       <c r="E54">
-        <v>-24.24810107106918</v>
+        <v>-20.30661692122107</v>
       </c>
       <c r="F54">
-        <v>-4.337908137979661</v>
+        <v>-4.256125564506369</v>
       </c>
       <c r="G54">
-        <v>-10.54463493326104</v>
+        <v>-8.006883281404088</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.07736989416900132</v>
       </c>
       <c r="E55">
-        <v>-24.52049783957857</v>
+        <v>-19.5417259620075</v>
       </c>
       <c r="F55">
-        <v>-5.063123501895439</v>
+        <v>-4.2975846098137</v>
       </c>
       <c r="G55">
-        <v>-10.54867710936449</v>
+        <v>-7.456177341491865</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.08698339697629501</v>
       </c>
       <c r="E56">
-        <v>-22.69577188055784</v>
+        <v>-19.25132398084361</v>
       </c>
       <c r="F56">
-        <v>-5.005692782430901</v>
+        <v>-4.53400735554712</v>
       </c>
       <c r="G56">
-        <v>-10.76503781308356</v>
+        <v>-7.93056196454173</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.1185131627995725</v>
       </c>
       <c r="E57">
-        <v>-23.2910352603921</v>
+        <v>-17.96688119873001</v>
       </c>
       <c r="F57">
-        <v>-4.544344995910151</v>
+        <v>-4.358791676033603</v>
       </c>
       <c r="G57">
-        <v>-10.36261782896637</v>
+        <v>-7.385675963687546</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.1700026843817377</v>
       </c>
       <c r="E58">
-        <v>-22.09690383541347</v>
+        <v>-17.92274669105126</v>
       </c>
       <c r="F58">
-        <v>-4.918642011229899</v>
+        <v>-4.5861801713724</v>
       </c>
       <c r="G58">
-        <v>-10.49348369413377</v>
+        <v>-8.230808581680391</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.2383932658151296</v>
       </c>
       <c r="E59">
-        <v>-23.08713618972273</v>
+        <v>-17.08597979238794</v>
       </c>
       <c r="F59">
-        <v>-4.817984830656398</v>
+        <v>-4.695731444367008</v>
       </c>
       <c r="G59">
-        <v>-10.89840645067864</v>
+        <v>-7.984060380456352</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.3203829608748042</v>
       </c>
       <c r="E60">
-        <v>-23.01529647806505</v>
+        <v>-17.30518510520323</v>
       </c>
       <c r="F60">
-        <v>-5.227938192809307</v>
+        <v>-4.859419328522041</v>
       </c>
       <c r="G60">
-        <v>-10.73850048004076</v>
+        <v>-8.763405837492799</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.4115425824618995</v>
       </c>
       <c r="E61">
-        <v>-22.09188628621297</v>
+        <v>-17.04580317099188</v>
       </c>
       <c r="F61">
-        <v>-5.061131199853817</v>
+        <v>-5.035992244005088</v>
       </c>
       <c r="G61">
-        <v>-11.5501734142682</v>
+        <v>-7.873938393638035</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.5065813882704104</v>
       </c>
       <c r="E62">
-        <v>-21.11131316696207</v>
+        <v>-17.26273518985533</v>
       </c>
       <c r="F62">
-        <v>-5.024085151079857</v>
+        <v>-4.4913288566849</v>
       </c>
       <c r="G62">
-        <v>-10.26142438346747</v>
+        <v>-8.346078466812274</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.5987588075992253</v>
       </c>
       <c r="E63">
-        <v>-20.53710266278947</v>
+        <v>-16.99720358794157</v>
       </c>
       <c r="F63">
-        <v>-5.330299440947821</v>
+        <v>-4.640206714971701</v>
       </c>
       <c r="G63">
-        <v>-11.37240042935487</v>
+        <v>-8.864556245899692</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.6806795177214309</v>
       </c>
       <c r="E64">
-        <v>-19.66088822704533</v>
+        <v>-17.44859734855214</v>
       </c>
       <c r="F64">
-        <v>-5.098573175106636</v>
+        <v>-4.73807578128107</v>
       </c>
       <c r="G64">
-        <v>-11.8742294749253</v>
+        <v>-9.264039776123546</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.7452606238933798</v>
       </c>
       <c r="E65">
-        <v>-21.26679832201543</v>
+        <v>-16.75213616006847</v>
       </c>
       <c r="F65">
-        <v>-5.091932696203198</v>
+        <v>-4.751947461394404</v>
       </c>
       <c r="G65">
-        <v>-11.00234764897514</v>
+        <v>-9.828411648021881</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.786565382508106</v>
       </c>
       <c r="E66">
-        <v>-20.53031900872598</v>
+        <v>-16.00802183960209</v>
       </c>
       <c r="F66">
-        <v>-5.379276338235743</v>
+        <v>-4.725035546773341</v>
       </c>
       <c r="G66">
-        <v>-12.26630400423226</v>
+        <v>-9.055727008610447</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.8003273723906106</v>
       </c>
       <c r="E67">
-        <v>-20.52091336821205</v>
+        <v>-15.72885500245123</v>
       </c>
       <c r="F67">
-        <v>-5.317330473206287</v>
+        <v>-5.237902870429252</v>
       </c>
       <c r="G67">
-        <v>-12.0799037376436</v>
+        <v>-9.888680129564312</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.7836274918677599</v>
       </c>
       <c r="E68">
-        <v>-20.22174878984332</v>
+        <v>-16.131363886149</v>
       </c>
       <c r="F68">
-        <v>-5.420686288659696</v>
+        <v>-5.014765833620453</v>
       </c>
       <c r="G68">
-        <v>-11.87228949523928</v>
+        <v>-8.583083732514238</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.735682274032375</v>
       </c>
       <c r="E69">
-        <v>-21.21549071150853</v>
+        <v>-16.15780564587979</v>
       </c>
       <c r="F69">
-        <v>-5.304644988823617</v>
+        <v>-5.541600651597583</v>
       </c>
       <c r="G69">
-        <v>-12.12571837736157</v>
+        <v>-9.536894939470278</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.6553066915516841</v>
       </c>
       <c r="E70">
-        <v>-19.93752817569991</v>
+        <v>-13.91395583202714</v>
       </c>
       <c r="F70">
-        <v>-5.266063537164639</v>
+        <v>-5.084971516851884</v>
       </c>
       <c r="G70">
-        <v>-12.00713794669042</v>
+        <v>-8.538927676111438</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.5411943547688058</v>
       </c>
       <c r="E71">
-        <v>-20.98343358945947</v>
+        <v>-14.67368885934598</v>
       </c>
       <c r="F71">
-        <v>-5.709916124437529</v>
+        <v>-5.300751447830509</v>
       </c>
       <c r="G71">
-        <v>-12.21764560589605</v>
+        <v>-9.943406757874005</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.3948808478442472</v>
       </c>
       <c r="E72">
-        <v>-19.15999824553092</v>
+        <v>-15.4667061706212</v>
       </c>
       <c r="F72">
-        <v>-5.498159598337079</v>
+        <v>-5.420654614541387</v>
       </c>
       <c r="G72">
-        <v>-11.96723925185112</v>
+        <v>-9.53375323175351</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.2171015083757876</v>
       </c>
       <c r="E73">
-        <v>-20.51461878934139</v>
+        <v>-16.09199333312632</v>
       </c>
       <c r="F73">
-        <v>-5.741539564157025</v>
+        <v>-4.969238247816358</v>
       </c>
       <c r="G73">
-        <v>-12.15347730170836</v>
+        <v>-8.936759244111196</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.01121038420407716</v>
       </c>
       <c r="E74">
-        <v>-20.32035631136035</v>
+        <v>-14.626465932394</v>
       </c>
       <c r="F74">
-        <v>-5.79166464823364</v>
+        <v>-5.358422098741237</v>
       </c>
       <c r="G74">
-        <v>-12.19593504824951</v>
+        <v>-8.932445603273527</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.2182706641628885</v>
       </c>
       <c r="E75">
-        <v>-19.75909724284968</v>
+        <v>-16.68807183828196</v>
       </c>
       <c r="F75">
-        <v>-5.948088073354552</v>
+        <v>-5.751447228364014</v>
       </c>
       <c r="G75">
-        <v>-11.94224463302962</v>
+        <v>-9.130148072333261</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.4709472010101508</v>
       </c>
       <c r="E76">
-        <v>-21.21938972762913</v>
+        <v>-17.03325476951663</v>
       </c>
       <c r="F76">
-        <v>-6.001217447552757</v>
+        <v>-5.247641869956247</v>
       </c>
       <c r="G76">
-        <v>-12.10951987803792</v>
+        <v>-9.574082297512911</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.744014937075258</v>
       </c>
       <c r="E77">
-        <v>-21.59442888799638</v>
+        <v>-16.15000761363858</v>
       </c>
       <c r="F77">
-        <v>-6.014400215592875</v>
+        <v>-5.634918147105979</v>
       </c>
       <c r="G77">
-        <v>-11.18272603322787</v>
+        <v>-9.600993722201647</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.036648725740415</v>
       </c>
       <c r="E78">
-        <v>-21.54891772421929</v>
+        <v>-17.74113224097364</v>
       </c>
       <c r="F78">
-        <v>-5.842732829182901</v>
+        <v>-5.604967892686146</v>
       </c>
       <c r="G78">
-        <v>-11.83287082950318</v>
+        <v>-8.926201914386461</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.349967384569571</v>
       </c>
       <c r="E79">
-        <v>-22.11980885694427</v>
+        <v>-16.82634879210617</v>
       </c>
       <c r="F79">
-        <v>-6.091936873506875</v>
+        <v>-5.661335153628467</v>
       </c>
       <c r="G79">
-        <v>-11.7847123235434</v>
+        <v>-8.561618155237603</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.68153576127732</v>
       </c>
       <c r="E80">
-        <v>-23.01334017729374</v>
+        <v>-17.41707916945876</v>
       </c>
       <c r="F80">
-        <v>-6.191906725713075</v>
+        <v>-5.550565218931927</v>
       </c>
       <c r="G80">
-        <v>-10.89855873577345</v>
+        <v>-8.944251008666567</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.032869756818466</v>
       </c>
       <c r="E81">
-        <v>-23.7348845833059</v>
+        <v>-19.06761284730044</v>
       </c>
       <c r="F81">
-        <v>-6.076677075158658</v>
+        <v>-6.084878296241762</v>
       </c>
       <c r="G81">
-        <v>-11.16476963422286</v>
+        <v>-9.324665796584219</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.404007590788057</v>
       </c>
       <c r="E82">
-        <v>-23.81177807195614</v>
+        <v>-19.41993718204521</v>
       </c>
       <c r="F82">
-        <v>-6.540078136398775</v>
+        <v>-5.611042988577771</v>
       </c>
       <c r="G82">
-        <v>-11.47743079713379</v>
+        <v>-7.760088732542499</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.790755371861724</v>
       </c>
       <c r="E83">
-        <v>-23.45141569584775</v>
+        <v>-19.89355669308543</v>
       </c>
       <c r="F83">
-        <v>-6.207456738170296</v>
+        <v>-5.974122614898461</v>
       </c>
       <c r="G83">
-        <v>-10.474957881296</v>
+        <v>-7.939622927682715</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.191322836320911</v>
       </c>
       <c r="E84">
-        <v>-24.90518264958215</v>
+        <v>-20.71807859803201</v>
       </c>
       <c r="F84">
-        <v>-6.489430429370064</v>
+        <v>-5.80204425680343</v>
       </c>
       <c r="G84">
-        <v>-11.40877339319485</v>
+        <v>-8.445153163166044</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.595533679439693</v>
       </c>
       <c r="E85">
-        <v>-25.52267630832007</v>
+        <v>-21.5901902363252</v>
       </c>
       <c r="F85">
-        <v>-6.44526720621212</v>
+        <v>-6.112074090148167</v>
       </c>
       <c r="G85">
-        <v>-10.41561304195903</v>
+        <v>-9.001016933028451</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.988133223223216</v>
       </c>
       <c r="E86">
-        <v>-27.16577876031516</v>
+        <v>-22.92407489765454</v>
       </c>
       <c r="F86">
-        <v>-6.705865222744723</v>
+        <v>-6.067611150645726</v>
       </c>
       <c r="G86">
-        <v>-11.50389860872026</v>
+        <v>-8.810908855435802</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>4.351844231337972</v>
       </c>
       <c r="E87">
-        <v>-27.85955909218629</v>
+        <v>-24.77925031590285</v>
       </c>
       <c r="F87">
-        <v>-6.910910003175542</v>
+        <v>-6.002120159924558</v>
       </c>
       <c r="G87">
-        <v>-11.2180330014042</v>
+        <v>-7.650863903565325</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.665575033883644</v>
       </c>
       <c r="E88">
-        <v>-28.42017511738787</v>
+        <v>-24.98560834795838</v>
       </c>
       <c r="F88">
-        <v>-6.434566105341496</v>
+        <v>-5.93385134902771</v>
       </c>
       <c r="G88">
-        <v>-10.92670499394833</v>
+        <v>-8.187751626396629</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>4.910957768223103</v>
       </c>
       <c r="E89">
-        <v>-29.93006797797333</v>
+        <v>-27.57541546210101</v>
       </c>
       <c r="F89">
-        <v>-6.76423072462585</v>
+        <v>-6.201384413764022</v>
       </c>
       <c r="G89">
-        <v>-10.25054262027989</v>
+        <v>-7.396762980698565</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.070896930284071</v>
       </c>
       <c r="E90">
-        <v>-32.007442030356</v>
+        <v>-27.79746918506713</v>
       </c>
       <c r="F90">
-        <v>-6.48711901058648</v>
+        <v>-6.395315537933244</v>
       </c>
       <c r="G90">
-        <v>-10.88559132889612</v>
+        <v>-8.023171165457303</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.131023713772526</v>
       </c>
       <c r="E91">
-        <v>-33.04878953502684</v>
+        <v>-29.92170615071817</v>
       </c>
       <c r="F91">
-        <v>-6.652282116801745</v>
+        <v>-5.798253656694826</v>
       </c>
       <c r="G91">
-        <v>-10.56673944582676</v>
+        <v>-7.415705922274275</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.079015317053415</v>
       </c>
       <c r="E92">
-        <v>-34.86739752566321</v>
+        <v>-31.55565429250676</v>
       </c>
       <c r="F92">
-        <v>-6.401020838493615</v>
+        <v>-6.316477865609711</v>
       </c>
       <c r="G92">
-        <v>-10.79342574108281</v>
+        <v>-8.667668171042617</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.90690593379828</v>
       </c>
       <c r="E93">
-        <v>-36.45083959684425</v>
+        <v>-34.2601201042866</v>
       </c>
       <c r="F93">
-        <v>-6.332883475187748</v>
+        <v>-5.578901677023928</v>
       </c>
       <c r="G93">
-        <v>-11.8310434083655</v>
+        <v>-8.450592389487065</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.611029957534305</v>
       </c>
       <c r="E94">
-        <v>-38.17308845330842</v>
+        <v>-35.79195568567624</v>
       </c>
       <c r="F94">
-        <v>-6.207493163406351</v>
+        <v>-5.227151882822292</v>
       </c>
       <c r="G94">
-        <v>-11.40484046509419</v>
+        <v>-9.086356175939782</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.191332078451889</v>
       </c>
       <c r="E95">
-        <v>-39.29362538295138</v>
+        <v>-37.39477962561011</v>
       </c>
       <c r="F95">
-        <v>-6.613190711837995</v>
+        <v>-5.269306966879459</v>
       </c>
       <c r="G95">
-        <v>-12.08545221196741</v>
+        <v>-8.368749082665204</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.648820121191423</v>
       </c>
       <c r="E96">
-        <v>-41.75031347516454</v>
+        <v>-39.48601307269325</v>
       </c>
       <c r="F96">
-        <v>-6.224727051178163</v>
+        <v>-5.141520112121523</v>
       </c>
       <c r="G96">
-        <v>-11.59683886418976</v>
+        <v>-9.314161435588112</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.005107077717509</v>
       </c>
       <c r="E97">
-        <v>-43.83833170570224</v>
+        <v>-42.27639082910962</v>
       </c>
       <c r="F97">
-        <v>-5.83222177302213</v>
+        <v>-4.913726188068375</v>
       </c>
       <c r="G97">
-        <v>-12.36130341902719</v>
+        <v>-10.40356596674162</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.25950958942417</v>
       </c>
       <c r="E98">
-        <v>-47.15465549031745</v>
+        <v>-43.82335604215887</v>
       </c>
       <c r="F98">
-        <v>-5.894828043418324</v>
+        <v>-5.044337582326497</v>
       </c>
       <c r="G98">
-        <v>-12.81548378265088</v>
+        <v>-10.36432607046464</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.46677568231124</v>
       </c>
       <c r="E99">
-        <v>-47.57324272097945</v>
+        <v>-46.4280369291797</v>
       </c>
       <c r="F99">
-        <v>-5.552122793699763</v>
+        <v>-4.629934006551203</v>
       </c>
       <c r="G99">
-        <v>-12.86266898822211</v>
+        <v>-10.64782463772013</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.6111745151065947</v>
       </c>
       <c r="E100">
-        <v>-50.04984477764134</v>
+        <v>-48.33491167093657</v>
       </c>
       <c r="F100">
-        <v>-5.555675837921051</v>
+        <v>-4.515267363449725</v>
       </c>
       <c r="G100">
-        <v>-13.11467433576251</v>
+        <v>-10.37702863369882</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.2059469257575557</v>
       </c>
       <c r="E101">
-        <v>-51.76700249720237</v>
+        <v>-51.80199628009665</v>
       </c>
       <c r="F101">
-        <v>-5.588901196174013</v>
+        <v>-4.122517006803277</v>
       </c>
       <c r="G101">
-        <v>-13.51535793874435</v>
+        <v>-11.36636861538232</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.068181715035983</v>
       </c>
       <c r="E102">
-        <v>-53.94498452449495</v>
+        <v>-53.35547343876893</v>
       </c>
       <c r="F102">
-        <v>-5.078443481068443</v>
+        <v>-3.598675393006329</v>
       </c>
       <c r="G102">
-        <v>-13.7904526861484</v>
+        <v>-11.3970772358046</v>
       </c>
     </row>
   </sheetData>
